--- a/United_Nations_in_Lebanon.xlsx
+++ b/United_Nations_in_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E424"/>
+  <dimension ref="A1:E426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -17799,6 +17799,73 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Statement on the Anniversary of the 4 August 2020 Beirut Port Explosion</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://lebanon.un.org/en/320485-statement-anniversary-4-august-2020-beirut-port-explosion</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2020-08-04</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Statement on the Anniversary of the 4 August 2020 Beirut Port Explosion
+04 August 2026
+Six years after the devastating Beirut Port explosion, time has not erased the pain of those whose lives were irrevocably changed in a matter of seconds, nor has it diminished the urgency of securing justice. Mr. Jean Arnault, Officer-in-Charge of the Office of the United Nations Special Coordinator for Lebanon (UNSCOL), expresses his unwavering solidarity with all those affected and pays tribute to their relentless pursuit of truth, justice, and accountability.
+Mr. Arnault stresses that a disaster of this magnitude cannot become an abandoned chapter in history. Rather, efforts must be redoubled to advance the judicial proceedings and bring them to a conclusive outcome. To this end, he calls on all relevant actors to take the necessary steps to facilitate swift progress in the case.
+“Despite the more recent security and humanitarian challenges facing Lebanon, the silent suffering of thousands who were directly or indirectly affected by this tragedy remains profound. Justice delayed is justice denied, and the right of victims, survivors, and all the people of Lebanon to accountability must be upheld without further delay,” he says.
+The Beirut Port explosion is a tragic reminder of broader institutional vulnerabilities. An impartial, independent and transparent judicial process is essential to breaking the cycle of impunity, restoring public trust, and upholding the rule of law. In this context, Mr. Arnault underscores the importance of advancing structural reforms to strengthen and safeguard the independence of the judiciary as a cornerstone of effective state-building and Lebanon’s reform agenda.
+On this somber occasion, the United Nations stands firmly alongside the people of Lebanon and affirms that the path towards genuine national recovery and the extension of the State’s authority is inextricably linked to the attainment of justice.</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:11:18.701444+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Statement of Jean Arnault, UNSCOL Officer-in-Charge, on the Occasion of Lebanon’s Army Day</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://lebanon.un.org/en/320448-statement-jean-arnault-unscol-officer-charge-occasion-lebanon%E2%80%99s-army-day</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Statement of Jean Arnault, UNSCOL Officer-in-Charge, on the Occasion of Lebanon’s Army Day
+01 August 2026
+- Beirut, 1 August 2026 -- Jean Arnault, Officer-in-Charge of the Office of the United Nations Special Coordinator for Lebanon (UNSCOL), congratulated the Lebanese Armed Forces (LAF), its Commander and servicemen and servicewomen on the occasion of the eighty-first army day, stressing that the army has earned the pride of the nation and the trust of the international community.
+As Lebanon strives to fulfill its national and international obligations, very high expectations fall on the Lebanese army, not least in advancing security and stability across the country, ensuring Lebanese territorial integrity and driving the implementation of United Nations Security Council resolution 1701 forward.
+“It is truly remarkable how the Lebanese army has succeeded in gaining the trust of the Lebanese people across communities and performing its daunting tasks in spite of a challenging operational environment and socio-economic difficulties,” Mr. Arnault stated.
+Both the achievements and challenges were showcased during a visit that Mr. Arnault carried out yesterday to the Lebanese army’s third land border regiment in eastern Lebanon, where he met with LAF personnel and toured a border post and watchtower. He reiterated the UN commitment to the mobilization of international support for the LAF.
+Reflecting on the positive perception of the LAF shared by the most diverse communities, including during his recent field visits across Lebanon, Mr. Arnault added:
+“Leadership, empathy and transparency are what people see in their army, and it is an inspiration for efforts to extend state authority throughout the country.”</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:11:20.791354+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
